--- a/public/exports-from-60/29188572.xlsx
+++ b/public/exports-from-60/29188572.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042241</t>
+          <t xml:space="preserve">200042252</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042241</t>
+          <t xml:space="preserve">200042252</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728669</t>
+          <t xml:space="preserve">311728670</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">

--- a/public/exports-from-60/29188572.xlsx
+++ b/public/exports-from-60/29188572.xlsx
@@ -10339,7 +10339,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056744</t>
+          <t xml:space="preserve">200056746</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311728670</t>
+          <t xml:space="preserve">311728669</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">

--- a/public/exports-from-60/29188572.xlsx
+++ b/public/exports-from-60/29188572.xlsx
@@ -9814,12 +9814,12 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042252</t>
+          <t xml:space="preserve">200042241</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200042252</t>
+          <t xml:space="preserve">200042241</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moe &amp; Brødsgaard A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056746</t>
+          <t xml:space="preserve">200056744</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
